--- a/Sim/tables_output_2035.xlsx
+++ b/Sim/tables_output_2035.xlsx
@@ -439,10 +439,10 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>1649</v>
+        <v>1510</v>
       </c>
       <c r="D2">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -453,10 +453,10 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>1673</v>
+        <v>1494</v>
       </c>
       <c r="D3">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -467,10 +467,10 @@
         <v>20</v>
       </c>
       <c r="C4">
-        <v>1695</v>
+        <v>1471</v>
       </c>
       <c r="D4">
-        <v>2.37</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -481,10 +481,10 @@
         <v>100</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D5">
-        <v>3.94</v>
+        <v>3.73</v>
       </c>
     </row>
   </sheetData>
@@ -519,10 +519,10 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>3116</v>
+        <v>2454</v>
       </c>
       <c r="D2">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -533,10 +533,10 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>3004</v>
+        <v>2368</v>
       </c>
       <c r="D3">
-        <v>2.87</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -547,10 +547,10 @@
         <v>20</v>
       </c>
       <c r="C4">
-        <v>2882</v>
+        <v>2269</v>
       </c>
       <c r="D4">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -613,10 +613,10 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>1543</v>
+        <v>1518</v>
       </c>
       <c r="D3">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -627,10 +627,10 @@
         <v>20</v>
       </c>
       <c r="C4">
-        <v>1527</v>
+        <v>1475</v>
       </c>
       <c r="D4">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -641,7 +641,7 @@
         <v>100</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D5">
         <v>1.46</v>
@@ -679,10 +679,10 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>4558</v>
+        <v>2789</v>
       </c>
       <c r="D2">
-        <v>4.42</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -693,10 +693,10 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>4398</v>
+        <v>2691</v>
       </c>
       <c r="D3">
-        <v>4.42</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -707,10 +707,10 @@
         <v>20</v>
       </c>
       <c r="C4">
-        <v>4213</v>
+        <v>2578</v>
       </c>
       <c r="D4">
-        <v>4.41</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -765,10 +765,10 @@
         <v>100</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E2">
-        <v>3.94</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -799,7 +799,7 @@
         <v>100</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E4">
         <v>1.46</v>
